--- a/docs/dashboard/data/보안접속이력.xlsx
+++ b/docs/dashboard/data/보안접속이력.xlsx
@@ -98,7 +98,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.0" customWidth="true"/>
@@ -150,22 +150,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:10</t>
+          <t>2026-08-28 12:58:20</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -175,34 +175,34 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:37:59</t>
+          <t>2026-08-28 12:57:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -212,34 +212,34 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:29:10</t>
+          <t>2026-08-28 12:57:15</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지티엑스에이운영(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>이성호</t>
+          <t/>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>backer@gtx-a.com</t>
+          <t>20200079@kgc.co.kr</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -249,34 +249,34 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>211.195.95.113</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:13:09</t>
+          <t>2026-08-28 12:55:45</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t/>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t/>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -286,34 +286,34 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 13:06:00</t>
+          <t>2026-08-28 10:55:30</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -328,29 +328,29 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 12:28:11</t>
+          <t>2026-08-28 10:15:25</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -365,14 +365,14 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 10:16:15</t>
+          <t>2026-08-28 09:24:34</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -409,22 +409,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 08:53:36</t>
+          <t>2026-08-28 09:08:03</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -439,29 +439,29 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 08:00:52</t>
+          <t>2026-08-27 16:47:59</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>주식회사 에이치엔에프</t>
+          <t>(주)대성티엠씨</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>조수형</t>
+          <t>유신재</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>whtngud17@hnfvac.com</t>
+          <t>daesungaero@hanmail.net</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -476,29 +476,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>125.240.4.243</t>
+          <t>220.92.133.242</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:40</t>
+          <t>2026-08-27 15:19:10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -513,29 +513,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:30</t>
+          <t>2026-08-27 14:37:59</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -545,34 +545,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:24</t>
+          <t>2026-08-27 14:29:10</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>지티엑스에이운영(주)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>이성호</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>backer@gtx-a.com</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -582,34 +582,34 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>211.195.95.113</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:18</t>
+          <t>2026-08-27 14:13:09</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -619,34 +619,34 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:57:49</t>
+          <t>2026-08-27 13:06:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>주식회사 브이티이코리아(VTE KOREA Co., Ltd)</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>사금석</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>gssa@vtekorea.com</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -661,29 +661,29 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>221.165.14.183</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:15:12</t>
+          <t>2026-08-27 12:28:11</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -698,29 +698,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:10:28</t>
+          <t>2026-08-27 10:16:15</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>주식회사 엑소퍼트(EXoPERT CORPORATION)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>전소희</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>s30211@exopert.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -735,29 +735,29 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>175.214.113.33</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:21:32</t>
+          <t>2026-08-27 08:53:36</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -767,34 +767,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:20:51</t>
+          <t>2026-08-27 08:00:52</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 에이치엔에프</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>조수형</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>whtngud17@hnfvac.com</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -804,34 +804,34 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>125.240.4.243</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:18:08</t>
+          <t>2026-08-26 18:57:40</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -841,34 +841,34 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:17:20</t>
+          <t>2026-08-26 18:57:30</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>kgc20200074@kgc.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -883,29 +883,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:41</t>
+          <t>2026-08-26 18:57:24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -920,29 +920,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:15</t>
+          <t>2026-08-26 18:57:18</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:06</t>
+          <t>2026-08-26 17:57:49</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 브이티이코리아(VTE KOREA Co., Ltd)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>사금석</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>gssa@vtekorea.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -989,34 +989,34 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>221.165.14.183</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:59</t>
+          <t>2026-08-26 17:15:12</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1026,34 +1026,34 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:47</t>
+          <t>2026-08-26 17:10:28</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 엑소퍼트(EXoPERT CORPORATION)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>전소희</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>s30211@exopert.com</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1063,19 +1063,19 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>175.214.113.33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:38</t>
+          <t>2026-08-26 16:21:32</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:16</t>
+          <t>2026-08-26 16:20:51</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1149,22 +1149,22 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:49</t>
+          <t>2026-08-26 16:18:08</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1174,34 +1174,34 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:18:37</t>
+          <t>2026-08-26 16:17:20</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t/>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t/>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>kgc20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1211,34 +1211,34 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:52:14</t>
+          <t>2026-08-26 16:16:41</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1248,34 +1248,34 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:51:14</t>
+          <t>2026-08-26 16:16:15</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1290,29 +1290,29 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:51:05</t>
+          <t>2026-08-26 16:16:06</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1327,29 +1327,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:56</t>
+          <t>2026-08-26 16:15:59</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1364,14 +1364,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:40</t>
+          <t>2026-08-26 16:15:47</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1401,14 +1401,14 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:34</t>
+          <t>2026-08-26 16:15:38</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1438,14 +1438,14 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:26</t>
+          <t>2026-08-26 16:15:16</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1475,29 +1475,29 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 13:36:45</t>
+          <t>2026-08-26 16:01:49</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1512,29 +1512,29 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 13:36:32</t>
+          <t>2026-08-26 15:18:37</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1544,34 +1544,34 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 12:29:18</t>
+          <t>2026-08-26 14:52:14</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1586,29 +1586,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 12:17:49</t>
+          <t>2026-08-26 14:51:14</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1618,34 +1618,34 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:35:34</t>
+          <t>2026-08-26 14:51:05</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1655,34 +1655,34 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:12:35</t>
+          <t>2026-08-26 14:50:56</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>neighbor1914@kic.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1697,29 +1697,29 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:46:59</t>
+          <t>2026-08-26 14:50:40</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t/>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t/>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1729,34 +1729,34 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:22:56</t>
+          <t>2026-08-26 14:50:34</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>케이젯정밀 (주) 밸브공장</t>
+          <t/>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>이샘솔</t>
+          <t/>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>leess@yppc.co.kr</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1766,19 +1766,19 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>211.195.112.19</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:30</t>
+          <t>2026-08-26 14:50:26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1808,29 +1808,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:24</t>
+          <t>2026-08-26 13:36:45</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1840,34 +1840,34 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.113.223.3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:21</t>
+          <t>2026-08-26 13:36:32</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1882,29 +1882,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.113.223.3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:13:26</t>
+          <t>2026-08-26 12:29:18</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1914,34 +1914,34 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:13:10</t>
+          <t>2026-08-26 12:17:49</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1951,34 +1951,34 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 08:43:04</t>
+          <t>2026-08-26 11:35:34</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1993,29 +1993,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:05:21</t>
+          <t>2026-08-26 11:12:35</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>(주)백콤</t>
+          <t/>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>서범석</t>
+          <t/>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>bsseo@vaccomp.com</t>
+          <t>neighbor1914@kic.co.kr</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2025,34 +2025,34 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>112.218.76.66</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 15:23:47</t>
+          <t>2026-08-26 10:46:59</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2067,29 +2067,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 14:27:44</t>
+          <t>2026-08-26 10:22:56</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>케이젯정밀 (주) 밸브공장</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이샘솔</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>zakutwo@kic21.co.kr</t>
+          <t>leess@yppc.co.kr</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2099,34 +2099,34 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.195.112.19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 13:40:10</t>
+          <t>2026-08-26 10:19:30</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2136,34 +2136,34 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:14:10</t>
+          <t>2026-08-26 10:19:24</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t/>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t/>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2173,34 +2173,34 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>118.130.171.169</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:13:22</t>
+          <t>2026-08-26 10:19:21</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>한국미쓰비시엘리베이터(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>장연욱</t>
+          <t/>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>ywjang@k-mec.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2210,34 +2210,34 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>180.68.169.230</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:08:00</t>
+          <t>2026-08-26 09:13:26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2247,19 +2247,19 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:27:04</t>
+          <t>2026-08-26 09:13:10</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2296,22 +2296,22 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:26:58</t>
+          <t>2026-08-26 08:43:04</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2321,34 +2321,34 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:26:35</t>
+          <t>2026-08-25 17:05:21</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)백콤</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>서범석</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>bsseo@vaccomp.com</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2358,34 +2358,34 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.218.76.66</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:25:51</t>
+          <t>2026-08-25 15:23:47</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>sh8683@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:20:11</t>
+          <t>2026-08-25 14:27:44</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>zakutwo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2432,34 +2432,34 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 17:39:25</t>
+          <t>2026-08-25 13:40:10</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2474,29 +2474,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 14:15:35</t>
+          <t>2026-08-25 11:14:10</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>sjh80@kic21.co.kr</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2506,34 +2506,34 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>118.130.171.169</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 13:50:39</t>
+          <t>2026-08-25 11:13:22</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>한국미쓰비시엘리베이터(주)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>장연욱</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>sjh80@kic21.co.kr</t>
+          <t>ywjang@k-mec.co.kr</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2543,34 +2543,34 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>180.68.169.230</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:26:23</t>
+          <t>2026-08-25 11:08:00</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2580,19 +2580,19 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:25:58</t>
+          <t>2026-08-25 09:27:04</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:25:49</t>
+          <t>2026-08-25 09:26:58</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:49:56</t>
+          <t>2026-08-25 09:26:35</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>yk9343@hanmail.net</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2696,66 +2696,66 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>112.219.197.250</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:46:43</t>
+          <t>2026-08-25 09:25:51</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>주식회사 웨이투웨이</t>
+          <t/>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>김미선</t>
+          <t/>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ms4564@wtwkorea.co.kr</t>
+          <t>sh8683@kic21.co.kr</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:45:13</t>
+          <t>2026-08-25 09:20:11</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>주식회사 웨이투웨이</t>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>김미선</t>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ms4564@wtwkorea.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2770,29 +2770,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 08:58:44</t>
+          <t>2026-08-24 17:39:25</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>kic@kic21.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2802,19 +2802,19 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 08:58:30</t>
+          <t>2026-08-24 14:15:35</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>kic@kic21.co.kr</t>
+          <t>sjh80@kic21.co.kr</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.230.14.120</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 18:18:28</t>
+          <t>2026-08-24 13:50:39</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>isr8380@daum.net</t>
+          <t>sjh80@kic21.co.kr</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2881,29 +2881,29 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>106.240.1.43</t>
+          <t>211.230.14.120</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:11:40</t>
+          <t>2026-08-24 11:26:23</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2913,34 +2913,34 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:12:18</t>
+          <t>2026-08-24 11:25:58</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2950,34 +2950,34 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:09:38</t>
+          <t>2026-08-24 11:25:49</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2987,34 +2987,34 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:59:06</t>
+          <t>2026-08-24 09:49:56</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>yk9343@hanmail.net</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3029,66 +3029,66 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.219.197.250</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:50</t>
+          <t>2026-08-24 09:46:43</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 웨이투웨이</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>김미선</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>ms4564@wtwkorea.co.kr</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:42</t>
+          <t>2026-08-24 09:45:13</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 웨이투웨이</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>김미선</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>ms4564@wtwkorea.co.kr</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3098,34 +3098,34 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:29</t>
+          <t>2026-08-24 08:58:44</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>kic@kic21.co.kr</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3140,29 +3140,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 14:15:09</t>
+          <t>2026-08-24 08:58:30</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t/>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t/>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>kic@kic21.co.kr</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3177,29 +3177,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 14:07:56</t>
+          <t>2026-08-21 18:18:28</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>(주)지에프에스</t>
+          <t/>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>임승현</t>
+          <t/>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>isr8380@daum.net</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3209,34 +3209,34 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>106.240.1.43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:14:02</t>
+          <t>2026-08-21 09:11:40</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3251,29 +3251,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:13:51</t>
+          <t>2026-08-21 08:12:18</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3283,34 +3283,34 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 09:45:46</t>
+          <t>2026-08-21 08:09:38</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>(주)디바이스</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>김용호</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>kimyh@deviceeng.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3325,29 +3325,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>211.194.154.158</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:24:20</t>
+          <t>2026-08-21 07:59:06</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3357,34 +3357,34 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:04:09</t>
+          <t>2026-08-21 07:58:50</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>(주)지에프에스</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>임승현</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3394,34 +3394,34 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:30:49</t>
+          <t>2026-08-21 07:58:42</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3431,34 +3431,34 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:01:55</t>
+          <t>2026-08-21 07:58:29</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3473,29 +3473,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:01:48</t>
+          <t>2026-08-20 14:15:09</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3510,29 +3510,29 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:56:13</t>
+          <t>2026-08-20 14:07:56</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)지에프에스</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>임승현</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3542,34 +3542,34 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:50:12</t>
+          <t>2026-08-20 10:14:02</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3584,29 +3584,29 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:30</t>
+          <t>2026-08-20 10:13:51</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>kkb9922@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3621,29 +3621,29 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:49:18</t>
+          <t>2026-08-20 09:45:46</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>(주)디바이스</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>김용호</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>kimyh@deviceeng.co.kr</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3658,29 +3658,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>211.194.154.158</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:44:27</t>
+          <t>2026-08-20 08:24:20</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3695,29 +3695,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 13:10:59</t>
+          <t>2026-08-20 08:04:09</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)지에프에스</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>임승현</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>lee389@kic21.co.kr</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3727,34 +3727,34 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 13:10:48</t>
+          <t>2026-08-19 17:30:49</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>KNSOK@kic21.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3764,34 +3764,34 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 11:07:04</t>
+          <t>2026-08-19 17:01:55</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3801,34 +3801,34 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:54:05</t>
+          <t>2026-08-19 17:01:48</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3838,34 +3838,34 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:06:13</t>
+          <t>2026-08-19 16:56:13</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3875,34 +3875,34 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:45:37</t>
+          <t>2026-08-19 16:50:12</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3917,66 +3917,66 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:45:02</t>
+          <t>2026-08-19 16:18:30</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>kkb9922@kic21.co.kr</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:51</t>
+          <t>2026-08-19 15:49:18</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3991,34 +3991,34 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:43</t>
+          <t>2026-08-19 15:44:27</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -4028,29 +4028,29 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:07</t>
+          <t>2026-08-19 13:10:59</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>lee389@kic21.co.kr</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4060,34 +4060,34 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:31:11</t>
+          <t>2026-08-19 13:10:48</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>에브제트아시아(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>전승헌</t>
+          <t/>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>sh.chun@avjet.kr</t>
+          <t>KNSOK@kic21.co.kr</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>221.151.167.29</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:57:13</t>
+          <t>2026-08-19 11:07:04</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4134,34 +4134,34 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:14</t>
+          <t>2026-08-19 10:54:05</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4171,34 +4171,34 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:10</t>
+          <t>2026-08-19 10:06:13</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4208,34 +4208,34 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:05</t>
+          <t>2026-08-19 09:45:37</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4245,71 +4245,71 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:51:53</t>
+          <t>2026-08-19 09:45:02</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:26:42</t>
+          <t>2026-08-19 09:44:51</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>(주)경인기술</t>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>임성종</t>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>tjdwhd8809@naver.com</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4324,34 +4324,34 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>218.145.248.145</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 17:28:18</t>
+          <t>2026-08-19 09:44:43</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -4361,29 +4361,29 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:56:52</t>
+          <t>2026-08-19 09:44:07</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4398,29 +4398,29 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:47:40</t>
+          <t>2026-08-19 09:31:11</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>에브제트아시아(주)</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>전승헌</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>sh.chun@avjet.kr</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -4435,29 +4435,29 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>221.151.167.29</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:46:27</t>
+          <t>2026-08-19 08:57:13</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4467,34 +4467,34 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 13:27:28</t>
+          <t>2026-08-19 08:56:14</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t/>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t/>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -4504,34 +4504,34 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>121.67.181.141</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 12:58:04</t>
+          <t>2026-08-19 08:56:10</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t/>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t/>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -4541,34 +4541,34 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>121.67.181.141</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:53:16</t>
+          <t>2026-08-19 08:56:05</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>씨트론(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>양혜원</t>
+          <t/>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>hyewon.yang@seetron.co.kr</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -4578,34 +4578,34 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>115.94.208.204</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:50:48</t>
+          <t>2026-08-19 08:51:53</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4615,39 +4615,39 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:50:14</t>
+          <t>2026-08-19 08:26:42</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)경인기술</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>임성종</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>tjdwhd8809@naver.com</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -4657,14 +4657,14 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>218.145.248.145</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:45:52</t>
+          <t>2026-08-18 17:28:18</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4701,22 +4701,22 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:19</t>
+          <t>2026-08-18 14:56:52</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -4731,29 +4731,29 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:02:46</t>
+          <t>2026-08-18 14:47:40</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>(주)알피바이오</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>노승우</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>nswok03@rpcorp.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4768,29 +4768,29 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>121.167.37.98</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:12:00</t>
+          <t>2026-08-18 14:46:27</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>주식회사 코젠바이오텍</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>정지만</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>stopman@kogene.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -4805,29 +4805,29 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>121.170.198.36</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:10:34</t>
+          <t>2026-08-18 13:27:28</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>(주)휴니드테크놀러지스</t>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>신원범</t>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>wbshin@huneed.com</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>222.98.239.225</t>
+          <t>121.67.181.141</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 08:32:15</t>
+          <t>2026-08-18 12:58:04</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -4879,29 +4879,29 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>121.67.181.141</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 08:30:15</t>
+          <t>2026-08-18 11:53:16</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>씨트론(주)</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>양혜원</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hyewon.yang@seetron.co.kr</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4916,29 +4916,29 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>115.94.208.204</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15 09:54:12</t>
+          <t>2026-08-18 11:50:48</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -4953,66 +4953,66 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:29:42</t>
+          <t>2026-08-18 11:50:14</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:29:20</t>
+          <t>2026-08-18 11:45:52</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -5022,34 +5022,34 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:08:53</t>
+          <t>2026-08-18 11:11:19</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>csyoo1496@kic21.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -5059,34 +5059,34 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 13:43:43</t>
+          <t>2026-08-18 11:02:46</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)알피바이오</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>노승우</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>calworld@hanmail.net</t>
+          <t>nswok03@rpcorp.co.kr</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -5096,34 +5096,34 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>121.167.37.98</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 11:33:23</t>
+          <t>2026-08-18 10:12:00</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 코젠바이오텍</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정지만</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>kic1@kic21.co.kr</t>
+          <t>stopman@kogene.co.kr</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5133,19 +5133,19 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.170.198.36</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:54:07</t>
+          <t>2026-08-18 10:10:34</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -5182,22 +5182,22 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:25:00</t>
+          <t>2026-08-18 08:32:15</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5207,34 +5207,34 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:24:53</t>
+          <t>2026-08-18 08:30:15</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5244,34 +5244,34 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:24:41</t>
+          <t>2026-08-15 09:54:12</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>210.113.223.3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:00:16</t>
+          <t>2026-08-14 10:29:42</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5318,34 +5318,34 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:00:01</t>
+          <t>2026-08-14 10:29:20</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -5360,29 +5360,29 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:59:01</t>
+          <t>2026-08-13 15:08:53</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>csyoo1496@kic21.co.kr</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -5392,34 +5392,34 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:13</t>
+          <t>2026-08-13 13:43:43</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>calworld@hanmail.net</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:50:01</t>
+          <t>2026-08-13 11:33:23</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>jcm2782@kic21.co.kr</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5471,29 +5471,29 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:48:44</t>
+          <t>2026-08-13 10:54:07</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)휴니드테크놀러지스</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>신원범</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>calworld@hanmail.net</t>
+          <t>wbshin@huneed.com</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5503,34 +5503,34 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>222.98.239.225</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12 10:03:25</t>
+          <t>2026-08-13 10:25:00</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5552,22 +5552,22 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12 10:02:15</t>
+          <t>2026-08-13 10:24:53</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 09:24:42</t>
+          <t>2026-08-13 10:24:41</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>vitamin-mk@nate.com</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5626,22 +5626,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:41:12</t>
+          <t>2026-08-13 10:00:16</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5651,34 +5651,34 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:32:26</t>
+          <t>2026-08-13 10:00:01</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -5693,29 +5693,29 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:31:04</t>
+          <t>2026-08-13 09:59:01</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5725,34 +5725,34 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:30:52</t>
+          <t>2026-08-13 09:16:13</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -5762,19 +5762,19 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 07:57:37</t>
+          <t>2026-08-13 08:50:01</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>jai7511@kic21.co.kr</t>
+          <t>jcm2782@kic21.co.kr</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5804,14 +5804,14 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:50</t>
+          <t>2026-08-13 08:48:44</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>jai7511@naver.com</t>
+          <t>calworld@hanmail.net</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -5841,14 +5841,14 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:08:40</t>
+          <t>2026-08-12 10:03:25</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>wtwkorea@wtwkorea.co.kr</t>
+          <t>cheekyguy@kic21.co.kr</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -5878,14 +5878,14 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:08:04</t>
+          <t>2026-08-12 10:02:15</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>jhnam@wtwkorea.co.kr</t>
+          <t>cheekyguy@kic21.co.kr</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -5915,14 +5915,14 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:55:20</t>
+          <t>2026-08-11 09:24:42</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>leejg8492@kic21.com</t>
+          <t>vitamin-mk@nate.com</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:03:21</t>
+          <t>2026-08-11 08:41:12</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>hwlee@kic21.co.kr</t>
+          <t>jh.ryoo@seoyoneh.com</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -5989,14 +5989,14 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:03:06</t>
+          <t>2026-08-11 08:32:26</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>temperature@kic21.co.kr</t>
+          <t>cheekyguy@kic21.co.kr</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:02:55</t>
+          <t>2026-08-11 08:31:04</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>gh1310@kic21.co.kr</t>
+          <t>jh.ryoo@seoyoneh.com</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 14:34:38</t>
+          <t>2026-08-11 08:30:52</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>min4103@kic21.co.kr</t>
+          <t>jh.ryoo@seoyoneh.com</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6100,42 +6100,375 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>2026-08-11 07:57:37</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>jai7511@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>211.230.14.120</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:15:50</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>jai7511@naver.com</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>211.230.14.120</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:40</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>wtwkorea@wtwkorea.co.kr</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>121.170.6.167</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:04</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>jhnam@wtwkorea.co.kr</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>121.170.6.167</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:55:20</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>leejg8492@kic21.com</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:21</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>hwlee@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:06</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>temperature@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:02:55</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>gh1310@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:34:38</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>min4103@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
           <t>2026-08-10 10:06:04</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>gh1310@kic21.co.kr</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>121.145.72.103</t>
         </is>

--- a/docs/dashboard/data/보안접속이력.xlsx
+++ b/docs/dashboard/data/보안접속이력.xlsx
@@ -98,7 +98,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="20.0" customWidth="true"/>
@@ -150,7 +150,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 12:58:20</t>
+          <t>2026-09-04 14:36:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -165,7 +165,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>dbshin@kiro.re.kr</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -180,29 +180,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>121.180.128.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 12:57:50</t>
+          <t>2026-09-04 14:28:13</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -212,34 +212,34 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 12:57:15</t>
+          <t>2026-09-03 16:27:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하이에어코리아(주)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>황동환</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20200079@kgc.co.kr</t>
+          <t>dhhwang@hiairkorea.co.kr</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -249,34 +249,34 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>59.21.233.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 12:55:45</t>
+          <t>2026-09-03 07:57:59</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하이에어코리아(주)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>황동환</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>dhhwang@hiairkorea.co.kr</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -286,39 +286,39 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>59.21.233.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 10:55:30</t>
+          <t>2026-09-03 07:57:44</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>하이에어코리아(주)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>황동환</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>dhhwang@hiairkorea.co.kr</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -328,29 +328,29 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>59.21.233.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 10:15:25</t>
+          <t>2026-09-03 07:56:37</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>디지트론</t>
+          <t>하이에어코리아(주)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>정재종</t>
+          <t>황동환</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>jjjeong@digitron.kr</t>
+          <t>dhhwang@hiairkorea.co.kr</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -365,29 +365,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>211.60.84.2</t>
+          <t>59.21.233.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 09:24:34</t>
+          <t>2026-09-02 15:46:08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -402,14 +402,14 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28 09:08:03</t>
+          <t>2026-09-02 13:44:23</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -434,34 +434,34 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>211.60.84.2</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 16:47:59</t>
+          <t>2026-09-02 13:42:38</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>(주)대성티엠씨</t>
+          <t/>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>유신재</t>
+          <t/>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>daesungaero@hanmail.net</t>
+          <t>kaeun3391@kic21.co.kr</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -471,34 +471,34 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>220.92.133.242</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:10</t>
+          <t>2026-09-02 13:42:10</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>kaeun3391@kic21.co.kr</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -508,34 +508,34 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:37:59</t>
+          <t>2026-09-02 13:41:48</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>kaeun3391@kic21.co.kr</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -545,34 +545,34 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:29:10</t>
+          <t>2026-09-02 13:41:40</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>지티엑스에이운영(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>이성호</t>
+          <t/>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>backer@gtx-a.com</t>
+          <t>kaeun3391@kic21.co.kr</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -582,34 +582,34 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>211.195.95.113</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 14:13:09</t>
+          <t>2026-09-02 11:37:23</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t/>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t/>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -619,34 +619,34 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 13:06:00</t>
+          <t>2026-09-02 11:37:09</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t/>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t/>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -656,34 +656,34 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 12:28:11</t>
+          <t>2026-09-02 11:34:40</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t/>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t/>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>kic21@kic21.co.kr</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -693,34 +693,34 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 10:16:15</t>
+          <t>2026-09-02 11:34:30</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>kic2@kic21.co.kr</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -730,34 +730,34 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 08:53:36</t>
+          <t>2026-09-02 11:34:23</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>kic@kic21.co.kr</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -767,34 +767,34 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27 08:00:52</t>
+          <t>2026-09-02 11:34:15</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>주식회사 에이치엔에프</t>
+          <t/>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>조수형</t>
+          <t/>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>whtngud17@hnfvac.com</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -804,34 +804,34 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>125.240.4.243</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:40</t>
+          <t>2026-09-02 11:34:03</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t/>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t/>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -841,34 +841,34 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:30</t>
+          <t>2026-09-02 11:33:11</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t/>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t/>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>wtw@kic21.co.kr</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -883,29 +883,29 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:24</t>
+          <t>2026-09-02 11:33:04</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t/>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t/>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>kic21@kic21.co.kr</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -920,29 +920,29 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:57:18</t>
+          <t>2026-09-02 10:13:37</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t/>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t/>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>kic1@kic21.co.kr</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:57:49</t>
+          <t>2026-09-02 08:30:56</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>주식회사 브이티이코리아(VTE KOREA Co., Ltd)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>사금석</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>gssa@vtekorea.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -994,29 +994,29 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>221.165.14.183</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:15:12</t>
+          <t>2026-09-01 17:08:24</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1031,29 +1031,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 17:10:28</t>
+          <t>2026-09-01 16:37:50</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>주식회사 엑소퍼트(EXoPERT CORPORATION)</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>전소희</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>s30211@exopert.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1068,29 +1068,29 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>175.214.113.33</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:21:32</t>
+          <t>2026-09-01 14:05:12</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1100,34 +1100,34 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:20:51</t>
+          <t>2026-09-01 13:37:13</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1137,34 +1137,34 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:18:08</t>
+          <t>2026-09-01 13:34:48</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1174,34 +1174,34 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:17:20</t>
+          <t>2026-09-01 13:02:56</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>kgc20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1211,71 +1211,71 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:41</t>
+          <t>2026-09-01 11:39:41</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:15</t>
+          <t>2026-09-01 11:39:34</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1285,34 +1285,34 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:16:06</t>
+          <t>2026-09-01 11:03:19</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1322,19 +1322,19 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:59</t>
+          <t>2026-08-31 16:08:23</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tg3885@naver.com</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1364,14 +1364,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>112.187.254.165</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:47</t>
+          <t>2026-08-31 16:08:10</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tg3885@naver.com</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1401,29 +1401,29 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>112.187.254.165</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:38</t>
+          <t>2026-08-31 16:05:22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1433,34 +1433,34 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:15:16</t>
+          <t>2026-08-31 11:57:42</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1470,19 +1470,19 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 16:01:49</t>
+          <t>2026-08-31 11:15:26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1519,22 +1519,22 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:18:37</t>
+          <t>2026-08-31 11:04:24</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1549,29 +1549,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:52:14</t>
+          <t>2026-08-31 10:37:42</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1586,29 +1586,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:51:14</t>
+          <t>2026-08-31 08:46:41</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1618,34 +1618,34 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:51:05</t>
+          <t>2026-08-31 08:27:23</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1655,34 +1655,34 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:56</t>
+          <t>2026-08-28 12:58:20</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1697,14 +1697,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:40</t>
+          <t>2026-08-28 12:57:50</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1734,14 +1734,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:34</t>
+          <t>2026-08-28 12:57:15</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200079@kgc.co.kr</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 14:50:26</t>
+          <t>2026-08-28 12:55:45</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>kimheymin5@gmail.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1808,29 +1808,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 13:36:45</t>
+          <t>2026-08-28 10:55:30</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1845,29 +1845,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 13:36:32</t>
+          <t>2026-08-28 10:15:25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1877,34 +1877,34 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 12:29:18</t>
+          <t>2026-08-28 09:24:34</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1919,29 +1919,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 12:17:49</t>
+          <t>2026-08-28 09:08:03</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>디지트론</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>정재종</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>jjjeong@digitron.kr</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1956,29 +1956,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>211.60.84.2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:35:34</t>
+          <t>2026-08-27 16:47:59</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>주식회사 파라타항공</t>
+          <t>(주)대성티엠씨</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>변태웅</t>
+          <t>유신재</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>tubyun@parataair.com</t>
+          <t>daesungaero@hanmail.net</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1993,29 +1993,29 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>210.220.69.242</t>
+          <t>220.92.133.242</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 11:12:35</t>
+          <t>2026-08-27 15:19:10</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>neighbor1914@kic.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2025,34 +2025,34 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:46:59</t>
+          <t>2026-08-27 14:37:59</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>대한약품공업(주)반월공장</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>이성원</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>won2847@daihan.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2067,29 +2067,29 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>210.182.141.241</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:22:56</t>
+          <t>2026-08-27 14:29:10</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>케이젯정밀 (주) 밸브공장</t>
+          <t>지티엑스에이운영(주)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>이샘솔</t>
+          <t>이성호</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>leess@yppc.co.kr</t>
+          <t>backer@gtx-a.com</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2104,29 +2104,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>211.195.112.19</t>
+          <t>211.195.95.113</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:30</t>
+          <t>2026-08-27 14:13:09</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2136,34 +2136,34 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:24</t>
+          <t>2026-08-27 13:06:00</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2173,34 +2173,34 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 10:19:21</t>
+          <t>2026-08-27 12:28:11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2210,34 +2210,34 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:13:26</t>
+          <t>2026-08-27 10:16:15</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2247,34 +2247,34 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 09:13:10</t>
+          <t>2026-08-27 08:53:36</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2284,34 +2284,34 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26 08:43:04</t>
+          <t>2026-08-27 08:00:52</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 에이치엔에프</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>조수형</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>whtngud17@hnfvac.com</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2326,29 +2326,29 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>125.240.4.243</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 17:05:21</t>
+          <t>2026-08-26 18:57:40</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>(주)백콤</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>서범석</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>bsseo@vaccomp.com</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2363,29 +2363,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>112.218.76.66</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 15:23:47</t>
+          <t>2026-08-26 18:57:30</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 14:27:44</t>
+          <t>2026-08-26 18:57:24</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>zakutwo@kic21.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2437,29 +2437,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 13:40:10</t>
+          <t>2026-08-26 18:57:18</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2469,34 +2469,34 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:14:10</t>
+          <t>2026-08-26 17:57:49</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t>주식회사 브이티이코리아(VTE KOREA Co., Ltd)</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t>사금석</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>gssa@vtekorea.com</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2511,29 +2511,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>118.130.171.169</t>
+          <t>221.165.14.183</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:13:22</t>
+          <t>2026-08-26 17:15:12</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>한국미쓰비시엘리베이터(주)</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>장연욱</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ywjang@k-mec.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2548,29 +2548,29 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>180.68.169.230</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 11:08:00</t>
+          <t>2026-08-26 17:10:28</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 엑소퍼트(EXoPERT CORPORATION)</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>전소희</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>s30211@exopert.com</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>175.214.113.33</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:27:04</t>
+          <t>2026-08-26 16:21:32</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2622,14 +2622,14 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:26:58</t>
+          <t>2026-08-26 16:20:51</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:26:35</t>
+          <t>2026-08-26 16:18:08</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>ncw5682@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2696,14 +2696,14 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:25:51</t>
+          <t>2026-08-26 16:17:20</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>sh8683@kic21.co.kr</t>
+          <t>kgc20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2733,29 +2733,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25 09:20:11</t>
+          <t>2026-08-26 16:16:41</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2765,34 +2765,34 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 17:39:25</t>
+          <t>2026-08-26 16:16:15</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2802,19 +2802,19 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 14:15:35</t>
+          <t>2026-08-26 16:16:06</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>sjh80@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 13:50:39</t>
+          <t>2026-08-26 16:15:59</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>sjh80@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2881,14 +2881,14 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:26:23</t>
+          <t>2026-08-26 16:15:47</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2918,14 +2918,14 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:25:58</t>
+          <t>2026-08-26 16:15:38</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2955,14 +2955,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:25:49</t>
+          <t>2026-08-26 16:15:16</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>rabbitbabo@kic21.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2992,29 +2992,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:49:56</t>
+          <t>2026-08-26 16:01:49</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>yk9343@hanmail.net</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -3024,39 +3024,39 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>112.219.197.250</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:46:43</t>
+          <t>2026-08-26 15:18:37</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>주식회사 웨이투웨이</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>김미선</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>ms4564@wtwkorea.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3066,29 +3066,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 09:45:13</t>
+          <t>2026-08-26 14:52:14</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>주식회사 웨이투웨이</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>김미선</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>ms4564@wtwkorea.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -3103,29 +3103,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 08:58:44</t>
+          <t>2026-08-26 14:51:14</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>kic@kic21.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -3140,29 +3140,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24 08:58:30</t>
+          <t>2026-08-26 14:51:05</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>kic@kic21.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -3177,29 +3177,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 18:18:28</t>
+          <t>2026-08-26 14:50:56</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>isr8380@daum.net</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -3214,29 +3214,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>106.240.1.43</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 09:11:40</t>
+          <t>2026-08-26 14:50:40</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3258,22 +3258,22 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:12:18</t>
+          <t>2026-08-26 14:50:34</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>김혜민</t>
+          <t/>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3295,22 +3295,22 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:09:38</t>
+          <t>2026-08-26 14:50:26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t/>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t/>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>kimheymin5@gmail.com</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3332,22 +3332,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:59:06</t>
+          <t>2026-08-26 13:36:45</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -3357,34 +3357,34 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>210.113.223.3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:50</t>
+          <t>2026-08-26 13:36:32</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>연합정밀(주)</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>하상우</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>swha@yeonhab.co.kr</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -3399,29 +3399,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>210.113.223.3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:42</t>
+          <t>2026-08-26 12:29:18</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -3431,34 +3431,34 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21 07:58:29</t>
+          <t>2026-08-26 12:17:49</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -3468,34 +3468,34 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 14:15:09</t>
+          <t>2026-08-26 11:35:34</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t>주식회사 파라타항공</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t>변태웅</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>tubyun@parataair.com</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3505,34 +3505,34 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.220.69.242</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 14:07:56</t>
+          <t>2026-08-26 11:12:35</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>(주)지에프에스</t>
+          <t/>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>임승현</t>
+          <t/>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>neighbor1914@kic.co.kr</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -3542,34 +3542,34 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:14:02</t>
+          <t>2026-08-26 10:46:59</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t>대한약품공업(주)반월공장</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t>이성원</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>won2847@daihan.com</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -3584,29 +3584,29 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>210.182.141.241</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 10:13:51</t>
+          <t>2026-08-26 10:22:56</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>(주)한국인삼공사</t>
+          <t>케이젯정밀 (주) 밸브공장</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>이건영</t>
+          <t>이샘솔</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>20200074@kgc.co.kr</t>
+          <t>leess@yppc.co.kr</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3616,34 +3616,34 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>211.250.138.4</t>
+          <t>211.195.112.19</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 09:45:46</t>
+          <t>2026-08-26 10:19:30</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>(주)디바이스</t>
+          <t/>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>김용호</t>
+          <t/>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>kimyh@deviceeng.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3653,34 +3653,34 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>211.194.154.158</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:24:20</t>
+          <t>2026-08-26 10:19:24</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3690,34 +3690,34 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20 08:04:09</t>
+          <t>2026-08-26 10:19:21</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>(주)지에프에스</t>
+          <t/>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>임승현</t>
+          <t/>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3727,34 +3727,34 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:30:49</t>
+          <t>2026-08-26 09:13:26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3764,19 +3764,19 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:01:55</t>
+          <t>2026-08-26 09:13:10</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -3813,22 +3813,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 17:01:48</t>
+          <t>2026-08-26 08:43:04</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>kic3@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3838,34 +3838,34 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:56:13</t>
+          <t>2026-08-25 17:05:21</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)백콤</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>서범석</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>hmkim@shinhwa-pritech.com</t>
+          <t>bsseo@vaccomp.com</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3875,34 +3875,34 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.218.76.66</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:50:12</t>
+          <t>2026-08-25 15:23:47</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 16:18:30</t>
+          <t>2026-08-25 14:27:44</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>kkb9922@kic21.co.kr</t>
+          <t>zakutwo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3954,29 +3954,29 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:49:18</t>
+          <t>2026-08-25 13:40:10</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3991,29 +3991,29 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 15:44:27</t>
+          <t>2026-08-25 11:14:10</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>(주)케이피씨엠</t>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>이예슬</t>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>ys-lee@kpccorp.co.kr</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -4028,29 +4028,29 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>210.183.114.237</t>
+          <t>118.130.171.169</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 13:10:59</t>
+          <t>2026-08-25 11:13:22</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>한국미쓰비시엘리베이터(주)</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>장연욱</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>lee389@kic21.co.kr</t>
+          <t>ywjang@k-mec.co.kr</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -4060,34 +4060,34 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>180.68.169.230</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 13:10:48</t>
+          <t>2026-08-25 11:08:00</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>KNSOK@kic21.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -4097,34 +4097,34 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 11:07:04</t>
+          <t>2026-08-25 09:27:04</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -4134,34 +4134,34 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:54:05</t>
+          <t>2026-08-25 09:26:58</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -4171,34 +4171,34 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 10:06:13</t>
+          <t>2026-08-25 09:26:35</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t/>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>ncw5682@kic21.co.kr</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -4208,34 +4208,34 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:45:37</t>
+          <t>2026-08-25 09:25:51</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>sh8683@kic21.co.kr</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -4245,39 +4245,39 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:45:02</t>
+          <t>2026-08-25 09:20:11</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>(주)한국기능공사</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>하갑봉</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>gbha@hkcb.co.kr</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -4287,29 +4287,29 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>211.54.242.146</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:51</t>
+          <t>2026-08-24 17:39:25</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -4324,66 +4324,66 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:43</t>
+          <t>2026-08-24 14:15:35</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>sjh80@kic21.co.kr</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>211.230.14.120</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:44:07</t>
+          <t>2026-08-24 13:50:39</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>(주)코리아하이텍</t>
+          <t/>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>박진우</t>
+          <t/>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>jwp97@koreahitek.co.kr</t>
+          <t>sjh80@kic21.co.kr</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -4393,34 +4393,34 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>112.216.103.122</t>
+          <t>211.230.14.120</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 09:31:11</t>
+          <t>2026-08-24 11:26:23</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>에브제트아시아(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>전승헌</t>
+          <t/>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>sh.chun@avjet.kr</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -4430,19 +4430,19 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>221.151.167.29</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:57:13</t>
+          <t>2026-08-24 11:25:58</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -4472,14 +4472,14 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:14</t>
+          <t>2026-08-24 11:25:49</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>skyies88@gfs.co.kr</t>
+          <t>rabbitbabo@kic21.co.kr</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -4509,14 +4509,14 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:10</t>
+          <t>2026-08-24 09:49:56</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>yk9343@hanmail.net</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -4546,66 +4546,66 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>112.219.197.250</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:56:05</t>
+          <t>2026-08-24 09:46:43</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 웨이투웨이</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김미선</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>ms4564@wtwkorea.co.kr</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:51:53</t>
+          <t>2026-08-24 09:45:13</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 웨이투웨이</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>김미선</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>koala88@naver.com</t>
+          <t>ms4564@wtwkorea.co.kr</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -4615,34 +4615,34 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>115.93.183.43</t>
+          <t>121.170.6.167</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19 08:26:42</t>
+          <t>2026-08-24 08:58:44</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>(주)경인기술</t>
+          <t/>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>임성종</t>
+          <t/>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>tjdwhd8809@naver.com</t>
+          <t>kic@kic21.co.kr</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -4652,34 +4652,34 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>218.145.248.145</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 17:28:18</t>
+          <t>2026-08-24 08:58:30</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t/>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t/>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>kic@kic21.co.kr</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -4689,34 +4689,34 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>118.36.239.10</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:56:52</t>
+          <t>2026-08-21 18:18:28</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t/>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t/>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>isr8380@daum.net</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -4726,34 +4726,34 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>106.240.1.43</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:47:40</t>
+          <t>2026-08-21 09:11:40</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -4768,29 +4768,29 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 14:46:27</t>
+          <t>2026-08-21 08:12:18</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>(주)에어로피스</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>염요찬</t>
+          <t>김혜민</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>ycyoum@aeropeace.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -4805,29 +4805,29 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1.215.239.154</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 13:27:28</t>
+          <t>2026-08-21 08:09:38</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -4842,29 +4842,29 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>121.67.181.141</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 12:58:04</t>
+          <t>2026-08-21 07:59:06</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>주식회사 덱스레보</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>이득훈</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>dh.lee@dexlevo.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -4874,34 +4874,34 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>121.67.181.141</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:53:16</t>
+          <t>2026-08-21 07:58:50</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>씨트론(주)</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>양혜원</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>hyewon.yang@seetron.co.kr</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -4911,34 +4911,34 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>115.94.208.204</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:50:48</t>
+          <t>2026-08-21 07:58:42</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>김호영</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>hoykim@caphmicro.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -4948,71 +4948,71 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:50:14</t>
+          <t>2026-08-21 07:58:29</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)신화프리텍</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>최문정</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>mjchoi@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>로그인</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:45:52</t>
+          <t>2026-08-20 14:15:09</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -5022,34 +5022,34 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:11:19</t>
+          <t>2026-08-20 14:07:56</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)지에프에스</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>임승현</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -5064,29 +5064,29 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 11:02:46</t>
+          <t>2026-08-20 10:14:02</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>(주)알피바이오</t>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>노승우</t>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>nswok03@rpcorp.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -5101,29 +5101,29 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>121.167.37.98</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:12:00</t>
+          <t>2026-08-20 10:13:51</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>주식회사 코젠바이오텍</t>
+          <t>(주)한국인삼공사</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>정지만</t>
+          <t>이건영</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>stopman@kogene.co.kr</t>
+          <t>20200074@kgc.co.kr</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -5133,34 +5133,34 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>성공</t>
+          <t>실패</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>121.170.198.36</t>
+          <t>211.250.138.4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 10:10:34</t>
+          <t>2026-08-20 09:45:46</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>(주)휴니드테크놀러지스</t>
+          <t>(주)디바이스</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>신원범</t>
+          <t>김용호</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>wbshin@huneed.com</t>
+          <t>kimyh@deviceeng.co.kr</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -5175,14 +5175,14 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>222.98.239.225</t>
+          <t>211.194.154.158</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 08:32:15</t>
+          <t>2026-08-20 08:24:20</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -5219,22 +5219,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18 08:30:15</t>
+          <t>2026-08-20 08:04:09</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>주식회사 카프마이크로</t>
+          <t>(주)지에프에스</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>박준영</t>
+          <t>임승현</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>jypark@caphmicro.com</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -5249,29 +5249,29 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>112.220.87.178</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15 09:54:12</t>
+          <t>2026-08-19 17:30:49</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -5286,29 +5286,29 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>210.113.223.3</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:29:42</t>
+          <t>2026-08-19 17:01:55</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t/>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -5323,29 +5323,29 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14 10:29:20</t>
+          <t>2026-08-19 17:01:48</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>연합정밀(주)</t>
+          <t/>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>하상우</t>
+          <t/>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>swha@yeonhab.co.kr</t>
+          <t>kic3@kic21.co.kr</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 15:08:53</t>
+          <t>2026-08-19 16:56:13</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>csyoo1496@kic21.co.kr</t>
+          <t>hmkim@shinhwa-pritech.com</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -5397,29 +5397,29 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>125.135.140.2</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 13:43:43</t>
+          <t>2026-08-19 16:50:12</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>calworld@hanmail.net</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -5429,19 +5429,19 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 11:33:23</t>
+          <t>2026-08-19 16:18:30</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>kic1@kic21.co.kr</t>
+          <t>kkb9922@kic21.co.kr</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -5471,29 +5471,29 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>121.145.72.103</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:54:07</t>
+          <t>2026-08-19 15:49:18</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>(주)휴니드테크놀러지스</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>신원범</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>wbshin@huneed.com</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -5508,29 +5508,29 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>222.98.239.225</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:25:00</t>
+          <t>2026-08-19 15:44:27</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>(주)케이피씨엠</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>이예슬</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>ys-lee@kpccorp.co.kr</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -5540,34 +5540,34 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>210.183.114.237</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:24:53</t>
+          <t>2026-08-19 13:10:59</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>lee389@kic21.co.kr</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -5589,22 +5589,22 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:24:41</t>
+          <t>2026-08-19 13:10:48</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t/>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t/>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>KNSOK@kic21.co.kr</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -5626,22 +5626,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:00:16</t>
+          <t>2026-08-19 11:07:04</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5656,29 +5656,29 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 10:00:01</t>
+          <t>2026-08-19 10:54:05</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -5688,34 +5688,34 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:59:01</t>
+          <t>2026-08-19 10:06:13</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>(주)한국기능공사</t>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>하갑봉</t>
+          <t>김호영</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>gbha@hkcb.co.kr</t>
+          <t>hoykim@caphmicro.com</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5730,29 +5730,29 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>211.54.242.146</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:13</t>
+          <t>2026-08-19 09:45:37</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>(주)신화프리텍</t>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>최문정</t>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>mjchoi@shinhwa-pritech.com</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -5767,66 +5767,66 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>125.135.140.2</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:50:01</t>
+          <t>2026-08-19 09:45:02</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>jcm2782@kic21.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13 08:48:44</t>
+          <t>2026-08-19 09:44:51</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>calworld@hanmail.net</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -5836,71 +5836,71 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12 10:03:25</t>
+          <t>2026-08-19 09:44:43</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12 10:02:15</t>
+          <t>2026-08-19 09:44:07</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)코리아하이텍</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박진우</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>jwp97@koreahitek.co.kr</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -5910,34 +5910,34 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>112.216.103.122</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 09:24:42</t>
+          <t>2026-08-19 09:31:11</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>에브제트아시아(주)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>전승헌</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>vitamin-mk@nate.com</t>
+          <t>sh.chun@avjet.kr</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -5947,19 +5947,19 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>221.151.167.29</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:41:12</t>
+          <t>2026-08-19 08:57:13</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -5989,14 +5989,14 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:32:26</t>
+          <t>2026-08-19 08:56:14</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>cheekyguy@kic21.co.kr</t>
+          <t>skyies88@gfs.co.kr</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:31:04</t>
+          <t>2026-08-19 08:56:10</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -6063,14 +6063,14 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 08:30:52</t>
+          <t>2026-08-19 08:56:05</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>jh.ryoo@seoyoneh.com</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -6100,14 +6100,14 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11 07:57:37</t>
+          <t>2026-08-19 08:51:53</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>jai7511@kic21.co.kr</t>
+          <t>koala88@naver.com</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -6137,29 +6137,29 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>115.93.183.43</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:15:50</t>
+          <t>2026-08-19 08:26:42</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)경인기술</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>임성종</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>jai7511@naver.com</t>
+          <t>tjdwhd8809@naver.com</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -6169,34 +6169,34 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>211.230.14.120</t>
+          <t>218.145.248.145</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:08:40</t>
+          <t>2026-08-18 17:28:18</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 카프마이크로</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>박준영</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>wtwkorea@wtwkorea.co.kr</t>
+          <t>jypark@caphmicro.com</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -6206,34 +6206,34 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>112.220.87.178</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 16:08:04</t>
+          <t>2026-08-18 14:56:52</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>jhnam@wtwkorea.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -6243,34 +6243,34 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>121.170.6.167</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:55:20</t>
+          <t>2026-08-18 14:47:40</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>leejg8492@kic21.com</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -6280,34 +6280,34 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>118.36.239.10</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:03:21</t>
+          <t>2026-08-18 14:46:27</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>(주)에어로피스</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>염요찬</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>hwlee@kic21.co.kr</t>
+          <t>ycyoum@aeropeace.co.kr</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -6317,34 +6317,34 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>1.215.239.154</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:03:06</t>
+          <t>2026-08-18 13:27:28</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>temperature@kic21.co.kr</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -6354,34 +6354,34 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>121.67.181.141</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 15:02:55</t>
+          <t>2026-08-18 12:58:04</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>주식회사 덱스레보</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>이득훈</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>gh1310@kic21.co.kr</t>
+          <t>dh.lee@dexlevo.com</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -6391,34 +6391,34 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>121.67.181.141</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10 14:34:38</t>
+          <t>2026-08-18 11:53:16</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>씨트론(주)</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>양혜원</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>min4103@kic21.co.kr</t>
+          <t>hyewon.yang@seetron.co.kr</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -6428,47 +6428,1564 @@
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>실패</t>
+          <t>성공</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>121.145.72.103</t>
+          <t>115.94.208.204</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>2026-08-18 11:50:48</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>김호영</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>hoykim@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 11:50:14</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 11:45:52</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 11:11:19</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 11:02:46</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>(주)알피바이오</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>노승우</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>nswok03@rpcorp.co.kr</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>121.167.37.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:12:00</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 코젠바이오텍</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>정지만</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>stopman@kogene.co.kr</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>121.170.198.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:10:34</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>(주)휴니드테크놀러지스</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>신원범</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>wbshin@huneed.com</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>222.98.239.225</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 08:32:15</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18 08:30:15</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>주식회사 카프마이크로</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>박준영</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>jypark@caphmicro.com</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>112.220.87.178</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15 09:54:12</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>연합정밀(주)</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>하상우</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>swha@yeonhab.co.kr</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>210.113.223.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:29:42</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>연합정밀(주)</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>하상우</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>swha@yeonhab.co.kr</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:29:20</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>연합정밀(주)</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>하상우</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>swha@yeonhab.co.kr</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 15:08:53</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>csyoo1496@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 13:43:43</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>calworld@hanmail.net</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 11:33:23</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>kic1@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:54:07</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>(주)휴니드테크놀러지스</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>신원범</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>wbshin@huneed.com</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>222.98.239.225</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:25:00</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:24:53</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:24:41</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00:16</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>211.54.242.146</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:00:01</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>211.54.242.146</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:59:01</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>(주)한국기능공사</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>하갑봉</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>gbha@hkcb.co.kr</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>211.54.242.146</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 09:16:13</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>(주)신화프리텍</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>최문정</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>mjchoi@shinhwa-pritech.com</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>성공</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>125.135.140.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:50:01</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>jcm2782@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:48:44</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>calworld@hanmail.net</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:03:25</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>cheekyguy@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:02:15</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>cheekyguy@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 09:24:42</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>vitamin-mk@nate.com</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:41:12</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>jh.ryoo@seoyoneh.com</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:32:26</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>cheekyguy@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:31:04</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>jh.ryoo@seoyoneh.com</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:30:52</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>jh.ryoo@seoyoneh.com</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11 07:57:37</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>jai7511@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>211.230.14.120</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:15:50</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>jai7511@naver.com</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>211.230.14.120</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:40</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>wtwkorea@wtwkorea.co.kr</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>121.170.6.167</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:08:04</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>jhnam@wtwkorea.co.kr</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>121.170.6.167</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:55:20</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>leejg8492@kic21.com</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>118.36.239.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:21</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>hwlee@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:03:06</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>temperature@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:02:55</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>gh1310@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:34:38</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>min4103@kic21.co.kr</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>121.145.72.103</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
           <t>2026-08-10 10:06:04</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>gh1310@kic21.co.kr</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
-        <is>
-          <t>로그인</t>
-        </is>
-      </c>
-      <c r="F172" s="2" t="inlineStr">
-        <is>
-          <t>실패</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>실패</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>121.145.72.103</t>
         </is>
